--- a/tests/fixtures/raw/CP01.xlsx
+++ b/tests/fixtures/raw/CP01.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -573,6 +573,11 @@
           <t>적용모델</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>개정일</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -621,6 +626,11 @@
         </is>
       </c>
       <c r="J4" s="4" t="n"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="n"/>
@@ -657,6 +667,11 @@
         </is>
       </c>
       <c r="J5" s="4" t="n"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="6" t="n"/>
@@ -701,6 +716,11 @@
         </is>
       </c>
       <c r="J6" s="4" t="n"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="n"/>
@@ -737,6 +757,11 @@
         </is>
       </c>
       <c r="J7" s="4" t="n"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="6" t="n"/>
@@ -781,6 +806,11 @@
         </is>
       </c>
       <c r="J8" s="4" t="n"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="n"/>
@@ -825,6 +855,11 @@
         </is>
       </c>
       <c r="J9" s="4" t="n"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="6" t="n"/>
@@ -873,6 +908,11 @@
           <t>M2</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="n"/>
@@ -917,6 +957,11 @@
         </is>
       </c>
       <c r="J11" s="4" t="n"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="n"/>
@@ -953,6 +998,11 @@
         </is>
       </c>
       <c r="J12" s="4" t="n"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="7" t="n"/>
@@ -989,6 +1039,11 @@
         </is>
       </c>
       <c r="J13" s="4" t="n"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -1029,6 +1084,11 @@
         </is>
       </c>
       <c r="J14" s="4" t="n"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -1076,6 +1136,11 @@
           <t>용접 조건 재설정 후 초도품 확인</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -1124,6 +1189,11 @@
         </is>
       </c>
       <c r="J16" s="4" t="n"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="D17" s="4" t="inlineStr">
@@ -1157,6 +1227,11 @@
         </is>
       </c>
       <c r="J17" s="4" t="n"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="D18" s="4" t="inlineStr">
@@ -1190,6 +1265,11 @@
         </is>
       </c>
       <c r="J18" s="4" t="n"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="D19" s="4" t="inlineStr">
@@ -1227,6 +1307,11 @@
           <t>M3</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="B20" s="4" t="inlineStr">
@@ -1270,6 +1355,11 @@
         </is>
       </c>
       <c r="J20" s="4" t="n"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="B21" s="6" t="n"/>
@@ -1305,6 +1395,11 @@
         </is>
       </c>
       <c r="J21" s="4" t="n"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="B22" s="7" t="n"/>
@@ -1340,6 +1435,11 @@
         </is>
       </c>
       <c r="J22" s="4" t="n"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
@@ -1383,6 +1483,11 @@
         </is>
       </c>
       <c r="J23" s="4" t="n"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="B24" s="7" t="n"/>
@@ -1418,6 +1523,11 @@
         </is>
       </c>
       <c r="J24" s="4" t="n"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
@@ -1461,6 +1571,11 @@
         </is>
       </c>
       <c r="J25" s="4" t="n"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="B26" s="7" t="n"/>
@@ -1496,6 +1611,11 @@
         </is>
       </c>
       <c r="J26" s="4" t="n"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="4" t="inlineStr">
@@ -1539,6 +1659,11 @@
         </is>
       </c>
       <c r="J27" s="4" t="n"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="7" t="n"/>
@@ -1574,6 +1699,11 @@
         </is>
       </c>
       <c r="J28" s="4" t="n"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="B29" s="4" t="inlineStr">
@@ -1617,6 +1747,11 @@
         </is>
       </c>
       <c r="J29" s="4" t="n"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="B30" s="7" t="n"/>
@@ -1652,6 +1787,11 @@
         </is>
       </c>
       <c r="J30" s="4" t="n"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="B31" s="4" t="inlineStr">
@@ -1695,6 +1835,11 @@
         </is>
       </c>
       <c r="J31" s="4" t="n"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="n"/>
@@ -1734,6 +1879,11 @@
         </is>
       </c>
       <c r="J32" s="4" t="n"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="7" t="n"/>
@@ -1773,6 +1923,11 @@
         </is>
       </c>
       <c r="J33" s="4" t="n"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -1780,6 +1935,7 @@
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="C29:C30"/>
     <mergeCell ref="B11:B14"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B20:B22"/>
@@ -1787,13 +1943,12 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B31:B33"/>
-    <mergeCell ref="A1:J1"/>
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="C20:C22"/>
     <mergeCell ref="C27:C28"/>
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="C11:C14"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A4:A13"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="A16:A33"/>
